--- a/artfynd/A 24201-2021 artfynd.xlsx
+++ b/artfynd/A 24201-2021 artfynd.xlsx
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117658612</v>
+        <v>117658590</v>
       </c>
       <c r="B10" t="n">
-        <v>90495</v>
+        <v>57287</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>422592</v>
+        <v>422611</v>
       </c>
       <c r="R10" t="n">
-        <v>7051884</v>
+        <v>7051905</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,6 +1602,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117658590</v>
+        <v>117658612</v>
       </c>
       <c r="B11" t="n">
-        <v>57287</v>
+        <v>90495</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>422611</v>
+        <v>422592</v>
       </c>
       <c r="R11" t="n">
-        <v>7051905</v>
+        <v>7051884</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,11 +1709,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117658610</v>
+        <v>117658616</v>
       </c>
       <c r="B17" t="n">
-        <v>79561</v>
+        <v>86816</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>422855</v>
+        <v>422729</v>
       </c>
       <c r="R17" t="n">
-        <v>7052109</v>
+        <v>7051482</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117658616</v>
+        <v>117658610</v>
       </c>
       <c r="B18" t="n">
-        <v>86816</v>
+        <v>79561</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,21 +2388,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>422729</v>
+        <v>422855</v>
       </c>
       <c r="R18" t="n">
-        <v>7051482</v>
+        <v>7052109</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3850,7 +3850,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117658584</v>
+        <v>117658587</v>
       </c>
       <c r="B32" t="n">
         <v>57287</v>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>422761</v>
+        <v>422583</v>
       </c>
       <c r="R32" t="n">
-        <v>7051475</v>
+        <v>7051997</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3957,7 +3957,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117658587</v>
+        <v>117658597</v>
       </c>
       <c r="B33" t="n">
         <v>57287</v>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>422583</v>
+        <v>422481</v>
       </c>
       <c r="R33" t="n">
-        <v>7051997</v>
+        <v>7052091</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4064,7 +4064,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117658597</v>
+        <v>117658584</v>
       </c>
       <c r="B34" t="n">
         <v>57287</v>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>422481</v>
+        <v>422761</v>
       </c>
       <c r="R34" t="n">
-        <v>7052091</v>
+        <v>7051475</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 24201-2021 artfynd.xlsx
+++ b/artfynd/A 24201-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117658603</v>
+        <v>117658584</v>
       </c>
       <c r="B2" t="n">
         <v>57287</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422552</v>
+        <v>422761</v>
       </c>
       <c r="R2" t="n">
-        <v>7052255</v>
+        <v>7051475</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117658592</v>
+        <v>117658610</v>
       </c>
       <c r="B3" t="n">
-        <v>57287</v>
+        <v>79561</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422559</v>
+        <v>422855</v>
       </c>
       <c r="R3" t="n">
-        <v>7051848</v>
+        <v>7052109</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117658578</v>
+        <v>117658612</v>
       </c>
       <c r="B4" t="n">
-        <v>57287</v>
+        <v>90495</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422822</v>
+        <v>422592</v>
       </c>
       <c r="R4" t="n">
-        <v>7052150</v>
+        <v>7051884</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117658596</v>
+        <v>117658586</v>
       </c>
       <c r="B5" t="n">
         <v>57287</v>
@@ -1036,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422493</v>
+        <v>422610</v>
       </c>
       <c r="R5" t="n">
-        <v>7051958</v>
+        <v>7051983</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1066,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre på 3 granar</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117658581</v>
+        <v>117658585</v>
       </c>
       <c r="B6" t="n">
         <v>57287</v>
@@ -1143,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422896</v>
+        <v>422745</v>
       </c>
       <c r="R6" t="n">
-        <v>7051560</v>
+        <v>7051477</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117658595</v>
+        <v>117658598</v>
       </c>
       <c r="B7" t="n">
         <v>57287</v>
@@ -1250,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>422519</v>
+        <v>422480</v>
       </c>
       <c r="R7" t="n">
-        <v>7051908</v>
+        <v>7052089</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre på 2 granar</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117658588</v>
+        <v>117658587</v>
       </c>
       <c r="B8" t="n">
         <v>57287</v>
@@ -1357,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>422553</v>
+        <v>422583</v>
       </c>
       <c r="R8" t="n">
-        <v>7051933</v>
+        <v>7051997</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117658615</v>
+        <v>117658599</v>
       </c>
       <c r="B9" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>422421</v>
+        <v>422446</v>
       </c>
       <c r="R9" t="n">
-        <v>7052157</v>
+        <v>7052121</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,6 +1490,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117658590</v>
+        <v>117658591</v>
       </c>
       <c r="B10" t="n">
         <v>57287</v>
@@ -1566,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>422611</v>
+        <v>422596</v>
       </c>
       <c r="R10" t="n">
-        <v>7051905</v>
+        <v>7051897</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117658612</v>
+        <v>117658583</v>
       </c>
       <c r="B11" t="n">
-        <v>90495</v>
+        <v>57287</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>422592</v>
+        <v>422763</v>
       </c>
       <c r="R11" t="n">
-        <v>7051884</v>
+        <v>7051474</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1704,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117658579</v>
+        <v>117658588</v>
       </c>
       <c r="B12" t="n">
         <v>57287</v>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>422880</v>
+        <v>422553</v>
       </c>
       <c r="R12" t="n">
-        <v>7052057</v>
+        <v>7051933</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117658585</v>
+        <v>117658596</v>
       </c>
       <c r="B13" t="n">
         <v>57287</v>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>422745</v>
+        <v>422493</v>
       </c>
       <c r="R13" t="n">
-        <v>7051477</v>
+        <v>7051958</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre på 3 granar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117658599</v>
+        <v>117658597</v>
       </c>
       <c r="B14" t="n">
         <v>57287</v>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>422446</v>
+        <v>422481</v>
       </c>
       <c r="R14" t="n">
-        <v>7052121</v>
+        <v>7052091</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117658591</v>
+        <v>117658613</v>
       </c>
       <c r="B15" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>422596</v>
+        <v>422662</v>
       </c>
       <c r="R15" t="n">
-        <v>7051897</v>
+        <v>7051736</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,11 +2132,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117658586</v>
+        <v>117658615</v>
       </c>
       <c r="B16" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,21 +2174,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2203,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>422610</v>
+        <v>422421</v>
       </c>
       <c r="R16" t="n">
-        <v>7051983</v>
+        <v>7052157</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2239,11 +2234,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117658616</v>
+        <v>117658582</v>
       </c>
       <c r="B17" t="n">
-        <v>86816</v>
+        <v>57287</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>422729</v>
+        <v>422773</v>
       </c>
       <c r="R17" t="n">
-        <v>7051482</v>
+        <v>7051459</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,6 +2336,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack något färskare och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2372,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117658610</v>
+        <v>117658592</v>
       </c>
       <c r="B18" t="n">
-        <v>79561</v>
+        <v>57287</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,21 +2383,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>422855</v>
+        <v>422559</v>
       </c>
       <c r="R18" t="n">
-        <v>7052109</v>
+        <v>7051848</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2448,6 +2443,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,7 +2474,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117658600</v>
+        <v>117658604</v>
       </c>
       <c r="B19" t="n">
         <v>57287</v>
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>422445</v>
+        <v>422612</v>
       </c>
       <c r="R19" t="n">
-        <v>7052227</v>
+        <v>7052200</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,7 +2581,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117658583</v>
+        <v>117658601</v>
       </c>
       <c r="B20" t="n">
         <v>57287</v>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>422763</v>
+        <v>422482</v>
       </c>
       <c r="R20" t="n">
-        <v>7051474</v>
+        <v>7052227</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2688,7 +2688,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117658593</v>
+        <v>117658602</v>
       </c>
       <c r="B21" t="n">
         <v>57287</v>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>422504</v>
+        <v>422538</v>
       </c>
       <c r="R21" t="n">
-        <v>7051848</v>
+        <v>7052254</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,7 +2795,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117658604</v>
+        <v>117658606</v>
       </c>
       <c r="B22" t="n">
         <v>57287</v>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>422612</v>
+        <v>422626</v>
       </c>
       <c r="R22" t="n">
-        <v>7052200</v>
+        <v>7052193</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2902,10 +2902,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117658598</v>
+        <v>117658614</v>
       </c>
       <c r="B23" t="n">
-        <v>57287</v>
+        <v>90517</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2918,21 +2918,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>422480</v>
+        <v>422556</v>
       </c>
       <c r="R23" t="n">
-        <v>7052089</v>
+        <v>7051846</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2978,11 +2978,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3009,7 +3004,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117658582</v>
+        <v>117658603</v>
       </c>
       <c r="B24" t="n">
         <v>57287</v>
@@ -3049,10 +3044,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>422773</v>
+        <v>422552</v>
       </c>
       <c r="R24" t="n">
-        <v>7051459</v>
+        <v>7052255</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,7 +3084,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack något färskare och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3116,10 +3111,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117658613</v>
+        <v>117658594</v>
       </c>
       <c r="B25" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3132,21 +3127,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3156,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>422662</v>
+        <v>422528</v>
       </c>
       <c r="R25" t="n">
-        <v>7051736</v>
+        <v>7051904</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3192,6 +3187,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3218,7 +3218,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117658602</v>
+        <v>117658581</v>
       </c>
       <c r="B26" t="n">
         <v>57287</v>
@@ -3258,10 +3258,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>422538</v>
+        <v>422896</v>
       </c>
       <c r="R26" t="n">
-        <v>7052254</v>
+        <v>7051560</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3325,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117658577</v>
+        <v>117658600</v>
       </c>
       <c r="B27" t="n">
-        <v>90499</v>
+        <v>57287</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>422798</v>
+        <v>422445</v>
       </c>
       <c r="R27" t="n">
-        <v>7051477</v>
+        <v>7052227</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3401,6 +3401,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,10 +3432,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117658594</v>
+        <v>117658616</v>
       </c>
       <c r="B28" t="n">
-        <v>57287</v>
+        <v>86816</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3443,21 +3448,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3467,10 +3472,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>422528</v>
+        <v>422729</v>
       </c>
       <c r="R28" t="n">
-        <v>7051904</v>
+        <v>7051482</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3503,11 +3508,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3534,7 +3534,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117658606</v>
+        <v>117658593</v>
       </c>
       <c r="B29" t="n">
         <v>57287</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>422626</v>
+        <v>422504</v>
       </c>
       <c r="R29" t="n">
-        <v>7052193</v>
+        <v>7051848</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,7 +3641,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117658601</v>
+        <v>117658579</v>
       </c>
       <c r="B30" t="n">
         <v>57287</v>
@@ -3681,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>422482</v>
+        <v>422880</v>
       </c>
       <c r="R30" t="n">
-        <v>7052227</v>
+        <v>7052057</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,10 +3748,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117658614</v>
+        <v>117658595</v>
       </c>
       <c r="B31" t="n">
-        <v>90517</v>
+        <v>57287</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3764,21 +3764,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>422556</v>
+        <v>422519</v>
       </c>
       <c r="R31" t="n">
-        <v>7051846</v>
+        <v>7051908</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3824,6 +3824,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre på 2 granar</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3850,7 +3855,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117658587</v>
+        <v>117658590</v>
       </c>
       <c r="B32" t="n">
         <v>57287</v>
@@ -3890,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>422583</v>
+        <v>422611</v>
       </c>
       <c r="R32" t="n">
-        <v>7051997</v>
+        <v>7051905</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3957,7 +3962,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117658597</v>
+        <v>117658578</v>
       </c>
       <c r="B33" t="n">
         <v>57287</v>
@@ -3997,10 +4002,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>422481</v>
+        <v>422822</v>
       </c>
       <c r="R33" t="n">
-        <v>7052091</v>
+        <v>7052150</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4064,10 +4069,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117658584</v>
+        <v>117658577</v>
       </c>
       <c r="B34" t="n">
-        <v>57287</v>
+        <v>90499</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4080,21 +4085,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4104,10 +4109,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>422761</v>
+        <v>422798</v>
       </c>
       <c r="R34" t="n">
-        <v>7051475</v>
+        <v>7051477</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4140,11 +4145,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 24201-2021 artfynd.xlsx
+++ b/artfynd/A 24201-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117658584</v>
+        <v>117658600</v>
       </c>
       <c r="B2" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422761</v>
+        <v>422445</v>
       </c>
       <c r="R2" t="n">
-        <v>7051475</v>
+        <v>7052227</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117658610</v>
+        <v>117658577</v>
       </c>
       <c r="B3" t="n">
-        <v>79561</v>
+        <v>90501</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422855</v>
+        <v>422798</v>
       </c>
       <c r="R3" t="n">
-        <v>7052109</v>
+        <v>7051477</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117658612</v>
+        <v>117658585</v>
       </c>
       <c r="B4" t="n">
-        <v>90495</v>
+        <v>57288</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422592</v>
+        <v>422745</v>
       </c>
       <c r="R4" t="n">
-        <v>7051884</v>
+        <v>7051477</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117658586</v>
+        <v>117658592</v>
       </c>
       <c r="B5" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422610</v>
+        <v>422559</v>
       </c>
       <c r="R5" t="n">
-        <v>7051983</v>
+        <v>7051848</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117658585</v>
+        <v>117658603</v>
       </c>
       <c r="B6" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422745</v>
+        <v>422552</v>
       </c>
       <c r="R6" t="n">
-        <v>7051477</v>
+        <v>7052255</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117658598</v>
+        <v>117658579</v>
       </c>
       <c r="B7" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>422480</v>
+        <v>422880</v>
       </c>
       <c r="R7" t="n">
-        <v>7052089</v>
+        <v>7052057</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117658587</v>
+        <v>117658601</v>
       </c>
       <c r="B8" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>422583</v>
+        <v>422482</v>
       </c>
       <c r="R8" t="n">
-        <v>7051997</v>
+        <v>7052227</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1422,7 @@
         <v>117658599</v>
       </c>
       <c r="B9" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117658591</v>
+        <v>117658615</v>
       </c>
       <c r="B10" t="n">
-        <v>57287</v>
+        <v>90519</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>422596</v>
+        <v>422421</v>
       </c>
       <c r="R10" t="n">
-        <v>7051897</v>
+        <v>7052157</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,11 +1602,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117658583</v>
+        <v>117658610</v>
       </c>
       <c r="B11" t="n">
-        <v>57287</v>
+        <v>79563</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>422763</v>
+        <v>422855</v>
       </c>
       <c r="R11" t="n">
-        <v>7051474</v>
+        <v>7052109</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,11 +1704,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117658588</v>
+        <v>117658587</v>
       </c>
       <c r="B12" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>422553</v>
+        <v>422583</v>
       </c>
       <c r="R12" t="n">
-        <v>7051933</v>
+        <v>7051997</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117658596</v>
+        <v>117658606</v>
       </c>
       <c r="B13" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>422493</v>
+        <v>422626</v>
       </c>
       <c r="R13" t="n">
-        <v>7051958</v>
+        <v>7052193</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1917,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre på 3 granar</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117658597</v>
+        <v>117658602</v>
       </c>
       <c r="B14" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1989,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>422481</v>
+        <v>422538</v>
       </c>
       <c r="R14" t="n">
-        <v>7052091</v>
+        <v>7052254</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117658613</v>
+        <v>117658591</v>
       </c>
       <c r="B15" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>422662</v>
+        <v>422596</v>
       </c>
       <c r="R15" t="n">
-        <v>7051736</v>
+        <v>7051897</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,6 +2127,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117658615</v>
+        <v>117658596</v>
       </c>
       <c r="B16" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2174,21 +2174,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>422421</v>
+        <v>422493</v>
       </c>
       <c r="R16" t="n">
-        <v>7052157</v>
+        <v>7051958</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,6 +2234,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre på 3 granar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117658582</v>
+        <v>117658595</v>
       </c>
       <c r="B17" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2300,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>422773</v>
+        <v>422519</v>
       </c>
       <c r="R17" t="n">
-        <v>7051459</v>
+        <v>7051908</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,7 +2345,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack något färskare och äldre</t>
+          <t>Ringhack färska till äldre på 2 granar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117658592</v>
+        <v>117658584</v>
       </c>
       <c r="B18" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2407,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>422559</v>
+        <v>422761</v>
       </c>
       <c r="R18" t="n">
-        <v>7051848</v>
+        <v>7051475</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2474,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117658604</v>
+        <v>117658598</v>
       </c>
       <c r="B19" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2514,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>422612</v>
+        <v>422480</v>
       </c>
       <c r="R19" t="n">
-        <v>7052200</v>
+        <v>7052089</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2581,10 +2586,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117658601</v>
+        <v>117658613</v>
       </c>
       <c r="B20" t="n">
-        <v>57287</v>
+        <v>90519</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2597,21 +2602,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2621,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>422482</v>
+        <v>422662</v>
       </c>
       <c r="R20" t="n">
-        <v>7052227</v>
+        <v>7051736</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2657,11 +2662,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,10 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117658602</v>
+        <v>117658590</v>
       </c>
       <c r="B21" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>422538</v>
+        <v>422611</v>
       </c>
       <c r="R21" t="n">
-        <v>7052254</v>
+        <v>7051905</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117658606</v>
+        <v>117658583</v>
       </c>
       <c r="B22" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>422626</v>
+        <v>422763</v>
       </c>
       <c r="R22" t="n">
-        <v>7052193</v>
+        <v>7051474</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2902,10 +2902,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117658614</v>
+        <v>117658604</v>
       </c>
       <c r="B23" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2918,21 +2918,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>422556</v>
+        <v>422612</v>
       </c>
       <c r="R23" t="n">
-        <v>7051846</v>
+        <v>7052200</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2978,6 +2978,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3004,10 +3009,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117658603</v>
+        <v>117658597</v>
       </c>
       <c r="B24" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3044,10 +3049,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>422552</v>
+        <v>422481</v>
       </c>
       <c r="R24" t="n">
-        <v>7052255</v>
+        <v>7052091</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3111,10 +3116,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117658594</v>
+        <v>117658582</v>
       </c>
       <c r="B25" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3151,10 +3156,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>422528</v>
+        <v>422773</v>
       </c>
       <c r="R25" t="n">
-        <v>7051904</v>
+        <v>7051459</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,7 +3196,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack något färskare och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3218,10 +3223,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117658581</v>
+        <v>117658614</v>
       </c>
       <c r="B26" t="n">
-        <v>57287</v>
+        <v>90519</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3234,21 +3239,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3258,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>422896</v>
+        <v>422556</v>
       </c>
       <c r="R26" t="n">
-        <v>7051560</v>
+        <v>7051846</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3294,11 +3299,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3325,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117658600</v>
+        <v>117658612</v>
       </c>
       <c r="B27" t="n">
-        <v>57287</v>
+        <v>90497</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>422445</v>
+        <v>422592</v>
       </c>
       <c r="R27" t="n">
-        <v>7052227</v>
+        <v>7051884</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3401,11 +3401,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3432,10 +3427,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117658616</v>
+        <v>117658578</v>
       </c>
       <c r="B28" t="n">
-        <v>86816</v>
+        <v>57288</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3448,21 +3443,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3472,10 +3467,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>422729</v>
+        <v>422822</v>
       </c>
       <c r="R28" t="n">
-        <v>7051482</v>
+        <v>7052150</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3508,6 +3503,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3534,10 +3534,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117658593</v>
+        <v>117658594</v>
       </c>
       <c r="B29" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>422504</v>
+        <v>422528</v>
       </c>
       <c r="R29" t="n">
-        <v>7051848</v>
+        <v>7051904</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,10 +3641,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117658579</v>
+        <v>117658616</v>
       </c>
       <c r="B30" t="n">
-        <v>57287</v>
+        <v>86818</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3657,21 +3657,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3681,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>422880</v>
+        <v>422729</v>
       </c>
       <c r="R30" t="n">
-        <v>7052057</v>
+        <v>7051482</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3717,11 +3717,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-06-07</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,10 +3743,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117658595</v>
+        <v>117658581</v>
       </c>
       <c r="B31" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3788,10 +3783,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>422519</v>
+        <v>422896</v>
       </c>
       <c r="R31" t="n">
-        <v>7051908</v>
+        <v>7051560</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3828,7 +3823,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre på 2 granar</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,10 +3850,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117658590</v>
+        <v>117658586</v>
       </c>
       <c r="B32" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3895,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>422611</v>
+        <v>422610</v>
       </c>
       <c r="R32" t="n">
-        <v>7051905</v>
+        <v>7051983</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3935,7 +3930,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3962,10 +3957,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117658578</v>
+        <v>117658588</v>
       </c>
       <c r="B33" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4002,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>422822</v>
+        <v>422553</v>
       </c>
       <c r="R33" t="n">
-        <v>7052150</v>
+        <v>7051933</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4069,10 +4064,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117658577</v>
+        <v>117658593</v>
       </c>
       <c r="B34" t="n">
-        <v>90499</v>
+        <v>57288</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4085,21 +4080,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4109,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>422798</v>
+        <v>422504</v>
       </c>
       <c r="R34" t="n">
-        <v>7051477</v>
+        <v>7051848</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4145,6 +4140,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
